--- a/data/fund.xlsx
+++ b/data/fund.xlsx
@@ -1,50 +1,109 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LLA\Documents\Angel Leus\database\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B4266C-114D-492A-8439-B1B98EDB9D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ledger" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Running Balance</t>
+  </si>
+  <si>
+    <t>Recorded By</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Surplus Sales</t>
+  </si>
+  <si>
+    <t>SAMPLE: Pre-order baskets sold</t>
+  </si>
+  <si>
+    <t>FUND TREASURER (UNASSIGNED)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Expense</t>
+  </si>
+  <si>
+    <t>Supplies</t>
+  </si>
+  <si>
+    <t>SAMPLE: School supplies for scholars</t>
+  </si>
+  <si>
+    <t>Entered as a positive number</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>SAMPLE: Transport assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUND TREASURER (UNASSIGNED) </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,85 +118,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -216,6 +212,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,6 +247,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -284,20 +282,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -419,179 +413,173 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="12.796875" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" customWidth="1"/>
+    <col min="3" max="3" width="20.796875" customWidth="1"/>
+    <col min="4" max="4" width="35.796875" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" customWidth="1"/>
+    <col min="6" max="6" width="15.796875" customWidth="1"/>
+    <col min="7" max="7" width="25.796875" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Running Balance</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Recorded By</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Surplus Sales</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE: Pre-order baskets sold</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
         <v>5000</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2">
         <v>5000</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>FUND TREASURER (UNASSIGNED)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE: School supplies for scholars</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
         <v>1200</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3">
         <v>3800</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>FUND TREASURER (UNASSIGNED)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Entered as a positive number</t>
-        </is>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Transportation</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE: Transport assistance</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4">
         <v>800</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4">
         <v>3000</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>FUND TREASURER (UNASSIGNED)</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H2 A4:H4 A3:F3 H3" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>